--- a/data/trans_bre/P6905-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Edad-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 52,0</t>
+          <t>1,34; 53,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 61,82</t>
+          <t>9,71; 69,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 55,93</t>
+          <t>-14,29; 54,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 74,42</t>
+          <t>10,57; 74,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 286,86</t>
+          <t>-0,86; 304,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,11; inf</t>
+          <t>-56,66; 801,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 24,59</t>
+          <t>-3,41; 23,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 21,88</t>
+          <t>-12,52; 21,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 37,63</t>
+          <t>3,15; 37,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 26,25</t>
+          <t>-18,78; 27,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 83,98</t>
+          <t>-9,11; 83,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 88,6</t>
+          <t>-33,32; 82,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 197,09</t>
+          <t>8,91; 205,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 92,35</t>
+          <t>-35,03; 101,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 24,28</t>
+          <t>-4,3; 24,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 36,7</t>
+          <t>6,79; 36,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 21,75</t>
+          <t>-7,22; 21,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 22,63</t>
+          <t>-2,03; 22,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 109,92</t>
+          <t>-13,49; 116,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 192,6</t>
+          <t>20,96; 179,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 95,72</t>
+          <t>-21,17; 92,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 171,92</t>
+          <t>-11,22; 158,91</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 24,98</t>
+          <t>-12,84; 24,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 29,72</t>
+          <t>-8,33; 29,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 28,31</t>
+          <t>-6,43; 25,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 23,41</t>
+          <t>-8,36; 23,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 103,33</t>
+          <t>-39,97; 106,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 147,53</t>
+          <t>-28,76; 164,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 128,69</t>
+          <t>-18,05; 115,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 170,9</t>
+          <t>-29,64; 160,25</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 36,99</t>
+          <t>-19,33; 36,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 43,28</t>
+          <t>-8,34; 41,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 49,62</t>
+          <t>2,97; 49,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 20,65</t>
+          <t>-4,08; 21,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,31; 178,09</t>
+          <t>-59,43; 169,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 307,8</t>
+          <t>-37,26; 311,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 294,94</t>
+          <t>4,9; 293,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 169,1</t>
+          <t>-19,18; 167,64</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,16</t>
+          <t>0,0; 81,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,36; 18,85</t>
+          <t>3,01; 18,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 23,46</t>
+          <t>5,79; 22,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 22,74</t>
+          <t>5,18; 22,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 17,46</t>
+          <t>-0,18; 17,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,35; 70,17</t>
+          <t>8,28; 67,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,45; 104,06</t>
+          <t>19,1; 100,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,03; 96,42</t>
+          <t>17,0; 94,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 91,13</t>
+          <t>-0,15; 89,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6905-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6905-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,09</t>
+          <t>43,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 53,6</t>
+          <t>3,48; 56,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 69,43</t>
+          <t>0,0; 60,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 54,2</t>
+          <t>-15,18; 55,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 74,8</t>
+          <t>11,48; 77,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 304,99</t>
+          <t>4,54; 297,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,66; 801,51</t>
+          <t>-54,25; 955,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>-5,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 23,73</t>
+          <t>-4,49; 22,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 21,15</t>
+          <t>-11,09; 22,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 37,42</t>
+          <t>2,78; 37,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 27,92</t>
+          <t>-25,72; 20,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 83,99</t>
+          <t>-10,59; 81,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 82,28</t>
+          <t>-27,79; 93,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 205,36</t>
+          <t>5,8; 196,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 101,39</t>
+          <t>-44,8; 60,52</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 24,06</t>
+          <t>-5,2; 23,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 36,95</t>
+          <t>7,51; 37,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 21,48</t>
+          <t>-5,59; 23,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 22,95</t>
+          <t>-3,78; 18,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 116,1</t>
+          <t>-17,46; 108,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,96; 179,25</t>
+          <t>22,4; 184,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 92,89</t>
+          <t>-17,62; 103,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 158,91</t>
+          <t>-14,42; 128,48</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,91</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 24,94</t>
+          <t>-13,34; 22,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 29,4</t>
+          <t>-7,03; 30,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 25,78</t>
+          <t>-7,07; 26,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 23,38</t>
+          <t>1,56; 23,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,97; 106,76</t>
+          <t>-39,6; 102,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 164,5</t>
+          <t>-25,25; 163,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 115,29</t>
+          <t>-21,94; 112,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 160,25</t>
+          <t>3,49; 155,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,45</t>
+          <t>6,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 36,33</t>
+          <t>-18,2; 37,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 41,58</t>
+          <t>-3,67; 43,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 49,08</t>
+          <t>3,07; 50,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 21,79</t>
+          <t>-5,9; 19,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,43; 169,5</t>
+          <t>-58,99; 192,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 311,26</t>
+          <t>-16,33; 363,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 293,96</t>
+          <t>8,44; 348,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 167,64</t>
+          <t>-21,22; 136,98</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,87</t>
+          <t>34,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,35</t>
+          <t>0,0; 86,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 18,75</t>
+          <t>2,9; 19,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 22,76</t>
+          <t>6,83; 24,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 22,52</t>
+          <t>5,42; 22,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 17,74</t>
+          <t>1,56; 15,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 67,27</t>
+          <t>8,99; 71,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,1; 100,31</t>
+          <t>22,47; 105,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,0; 94,61</t>
+          <t>16,84; 95,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 89,57</t>
+          <t>4,93; 71,85</t>
         </is>
       </c>
     </row>
